--- a/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05880000000000001</v>
+        <v>0.0767</v>
       </c>
       <c r="E2">
-        <v>-0.0287</v>
+        <v>0.29285</v>
       </c>
       <c r="F2">
-        <v>0.3395</v>
+        <v>0.157</v>
       </c>
       <c r="G2">
-        <v>0.04493855334673371</v>
+        <v>0.07313435871742414</v>
       </c>
       <c r="H2">
-        <v>0.04493855334673371</v>
+        <v>0.07313435871742414</v>
       </c>
       <c r="I2">
-        <v>0.05587251507542114</v>
+        <v>0.04565196678260851</v>
       </c>
       <c r="J2">
-        <v>0.04545821353378299</v>
+        <v>0.03688251330371068</v>
       </c>
       <c r="K2">
-        <v>3873.6</v>
+        <v>3941.9</v>
       </c>
       <c r="L2">
-        <v>0.03790727123623346</v>
+        <v>0.04220047554355099</v>
       </c>
       <c r="M2">
-        <v>2156.24</v>
+        <v>2031.24</v>
       </c>
       <c r="N2">
-        <v>0.0336146715763152</v>
+        <v>0.0294317773475988</v>
       </c>
       <c r="O2">
-        <v>0.5566501445683602</v>
+        <v>0.5152946548618688</v>
       </c>
       <c r="P2">
-        <v>2156.24</v>
+        <v>2031.24</v>
       </c>
       <c r="Q2">
-        <v>0.0336146715763152</v>
+        <v>0.0294317773475988</v>
       </c>
       <c r="R2">
-        <v>0.5566501445683602</v>
+        <v>0.5152946548618688</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9207.5</v>
+        <v>7819.6</v>
       </c>
       <c r="V2">
-        <v>0.1435401850160104</v>
+        <v>0.1133025768236562</v>
       </c>
       <c r="W2">
-        <v>0.08678193830547185</v>
+        <v>0.08536112575074323</v>
       </c>
       <c r="X2">
-        <v>0.08019723273388235</v>
+        <v>0.1102545877570397</v>
       </c>
       <c r="Y2">
-        <v>0.006584705571589494</v>
+        <v>-0.02489346200629647</v>
       </c>
       <c r="Z2">
-        <v>2.218473128317575</v>
+        <v>2.018443008187528</v>
       </c>
       <c r="AA2">
-        <v>0.1027016639255454</v>
+        <v>0.08011572275217903</v>
       </c>
       <c r="AB2">
-        <v>0.07033849111787546</v>
+        <v>0.1004196396845229</v>
       </c>
       <c r="AC2">
-        <v>0.03236317280766995</v>
+        <v>-0.02030391693234391</v>
       </c>
       <c r="AD2">
-        <v>11173.8</v>
+        <v>9538.099999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11173.8</v>
+        <v>9538.099999999999</v>
       </c>
       <c r="AG2">
-        <v>1966.299999999999</v>
+        <v>1718.499999999998</v>
       </c>
       <c r="AH2">
-        <v>0.148351823429758</v>
+        <v>0.1214220153704555</v>
       </c>
       <c r="AI2">
-        <v>0.185554273188472</v>
+        <v>0.2426491164693372</v>
       </c>
       <c r="AJ2">
-        <v>0.02974190806221553</v>
+        <v>0.02429535002410447</v>
       </c>
       <c r="AK2">
-        <v>0.03854658799082549</v>
+        <v>0.05457530661890329</v>
       </c>
       <c r="AL2">
-        <v>650.8</v>
+        <v>615.3</v>
       </c>
       <c r="AM2">
-        <v>650.8</v>
+        <v>615.3</v>
       </c>
       <c r="AN2">
-        <v>1.806246160809543</v>
+        <v>2.034968317296409</v>
       </c>
       <c r="AO2">
-        <v>8.772894898586355</v>
+        <v>6.93044043555989</v>
       </c>
       <c r="AP2">
-        <v>0.3178526397465324</v>
+        <v>0.3666446203409354</v>
       </c>
       <c r="AQ2">
-        <v>8.772894898586355</v>
+        <v>6.93044043555989</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft Aktiengesellschaft in München (XTRA:MUV2)</t>
+          <t>Hannover Rück SE (XTRA:HNR1)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.025</v>
+        <v>0.121</v>
       </c>
       <c r="E3">
-        <v>-0.04219999999999999</v>
+        <v>0.0607</v>
       </c>
       <c r="F3">
-        <v>0.481</v>
+        <v>0.17</v>
       </c>
       <c r="G3">
-        <v>0.04023076712253679</v>
+        <v>0.07987798712460818</v>
       </c>
       <c r="H3">
-        <v>0.04023076712253679</v>
+        <v>0.07987798712460818</v>
       </c>
       <c r="I3">
-        <v>0.05025214459944638</v>
+        <v>0.06757895446425562</v>
       </c>
       <c r="J3">
-        <v>0.04420080407497819</v>
+        <v>0.05405747715859947</v>
       </c>
       <c r="K3">
-        <v>2632.1</v>
+        <v>1221.8</v>
       </c>
       <c r="L3">
-        <v>0.03606901088058761</v>
+        <v>0.04118103070545013</v>
       </c>
       <c r="M3">
-        <v>1597.14</v>
+        <v>532.2</v>
       </c>
       <c r="N3">
-        <v>0.03865089467646931</v>
+        <v>0.02226023816196185</v>
       </c>
       <c r="O3">
-        <v>0.6067930549751149</v>
+        <v>0.4355868390898675</v>
       </c>
       <c r="P3">
-        <v>1597.14</v>
+        <v>532.2</v>
       </c>
       <c r="Q3">
-        <v>0.03865089467646931</v>
+        <v>0.02226023816196185</v>
       </c>
       <c r="R3">
-        <v>0.6067930549751149</v>
+        <v>0.4355868390898675</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7252</v>
+        <v>1610.5</v>
       </c>
       <c r="V3">
-        <v>0.1754988843769209</v>
+        <v>0.06736210740293039</v>
       </c>
       <c r="W3">
-        <v>0.0758748918996829</v>
+        <v>0.09239820920805855</v>
       </c>
       <c r="X3">
-        <v>0.078733205550178</v>
+        <v>0.1119088828634695</v>
       </c>
       <c r="Y3">
-        <v>-0.002858313650495103</v>
+        <v>-0.01951067365541098</v>
       </c>
       <c r="Z3">
-        <v>2.354501280917873</v>
+        <v>1.829838411249537</v>
       </c>
       <c r="AA3">
-        <v>0.1040708498121361</v>
+        <v>0.09891644812004981</v>
       </c>
       <c r="AB3">
-        <v>0.07074019164876627</v>
+        <v>0.09976178170233886</v>
       </c>
       <c r="AC3">
-        <v>0.03333065816336979</v>
+        <v>-0.000845333582289054</v>
       </c>
       <c r="AD3">
-        <v>6131.2</v>
+        <v>4445.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6131.2</v>
+        <v>4445.9</v>
       </c>
       <c r="AG3">
-        <v>-1120.8</v>
+        <v>2835.4</v>
       </c>
       <c r="AH3">
-        <v>0.1292046513000122</v>
+        <v>0.1567997460675742</v>
       </c>
       <c r="AI3">
-        <v>0.1496674030586713</v>
+        <v>0.3364588536227278</v>
       </c>
       <c r="AJ3">
-        <v>-0.02787962608267375</v>
+        <v>0.1060220240432254</v>
       </c>
       <c r="AK3">
-        <v>-0.03324484257048364</v>
+        <v>0.2443615178440616</v>
       </c>
       <c r="AL3">
-        <v>397.5</v>
+        <v>289.7</v>
       </c>
       <c r="AM3">
-        <v>397.5</v>
+        <v>289.7</v>
       </c>
       <c r="AN3">
-        <v>1.530007735882015</v>
+        <v>2.026667274467794</v>
       </c>
       <c r="AO3">
-        <v>9.225408805031446</v>
+        <v>6.92095270969969</v>
       </c>
       <c r="AP3">
-        <v>-0.2796895665410626</v>
+        <v>1.292519487623649</v>
       </c>
       <c r="AQ3">
-        <v>9.225408805031446</v>
+        <v>6.92095270969969</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hannover Rück SE (XTRA:HNR1)</t>
+          <t>Münchener Rückversicherungs-Gesellschaft Aktiengesellschaft in München (XTRA:MUV2)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,49 +862,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0926</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="E4">
-        <v>-0.0152</v>
+        <v>0.525</v>
       </c>
       <c r="F4">
-        <v>0.198</v>
+        <v>0.144</v>
       </c>
       <c r="G4">
-        <v>0.05669891346766077</v>
+        <v>0.06999540319329023</v>
       </c>
       <c r="H4">
-        <v>0.05669891346766077</v>
+        <v>0.06999540319329023</v>
       </c>
       <c r="I4">
-        <v>0.06991257077522404</v>
+        <v>0.03544561569754581</v>
       </c>
       <c r="J4">
-        <v>0.05226884357695669</v>
+        <v>0.02891996515310861</v>
       </c>
       <c r="K4">
-        <v>1241.5</v>
+        <v>2720.1</v>
       </c>
       <c r="L4">
-        <v>0.04249936670295287</v>
+        <v>0.04267499635236328</v>
       </c>
       <c r="M4">
-        <v>559.1</v>
+        <v>1499.04</v>
       </c>
       <c r="N4">
-        <v>0.02449657372193694</v>
+        <v>0.03323290568447097</v>
       </c>
       <c r="O4">
-        <v>0.4503423278292388</v>
+        <v>0.5510973861255102</v>
       </c>
       <c r="P4">
-        <v>559.1</v>
+        <v>1499.04</v>
       </c>
       <c r="Q4">
-        <v>0.02449657372193694</v>
+        <v>0.03323290568447097</v>
       </c>
       <c r="R4">
-        <v>0.4503423278292388</v>
+        <v>0.5510973861255102</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -913,73 +913,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1955.5</v>
+        <v>6209.1</v>
       </c>
       <c r="V4">
-        <v>0.0856788587251792</v>
+        <v>0.1376523873181827</v>
       </c>
       <c r="W4">
-        <v>0.09768898471126078</v>
+        <v>0.07832404229342792</v>
       </c>
       <c r="X4">
-        <v>0.0816612599175867</v>
+        <v>0.1086002926506099</v>
       </c>
       <c r="Y4">
-        <v>0.01602772479367408</v>
+        <v>-0.03027625035718196</v>
       </c>
       <c r="Z4">
-        <v>1.938678400063711</v>
+        <v>2.120161523698015</v>
       </c>
       <c r="AA4">
-        <v>0.1013324780389548</v>
+        <v>0.06131499738430824</v>
       </c>
       <c r="AB4">
-        <v>0.06993679058698465</v>
+        <v>0.101077497666707</v>
       </c>
       <c r="AC4">
-        <v>0.03139568745197011</v>
+        <v>-0.03976250028239876</v>
       </c>
       <c r="AD4">
-        <v>5042.6</v>
+        <v>5092.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5042.6</v>
+        <v>5092.2</v>
       </c>
       <c r="AG4">
-        <v>3087.1</v>
+        <v>-1116.900000000001</v>
       </c>
       <c r="AH4">
-        <v>0.1809575758445716</v>
+        <v>0.1014396615092242</v>
       </c>
       <c r="AI4">
-        <v>0.2619124292318081</v>
+        <v>0.1951453185357778</v>
       </c>
       <c r="AJ4">
-        <v>0.1191438286113459</v>
+        <v>-0.02538974589795001</v>
       </c>
       <c r="AK4">
-        <v>0.1784708772944067</v>
+        <v>-0.0561671184241626</v>
       </c>
       <c r="AL4">
-        <v>253.3</v>
+        <v>325.6</v>
       </c>
       <c r="AM4">
-        <v>253.3</v>
+        <v>325.6</v>
       </c>
       <c r="AN4">
-        <v>2.314287025563358</v>
+        <v>2.042271597016122</v>
       </c>
       <c r="AO4">
-        <v>8.062771417291748</v>
+        <v>6.938882063882064</v>
       </c>
       <c r="AP4">
-        <v>1.4168158244986</v>
+        <v>-0.4479425683805248</v>
       </c>
       <c r="AQ4">
-        <v>8.062771417291748</v>
+        <v>6.938882063882064</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0767</v>
+        <v>0.08995</v>
       </c>
       <c r="E2">
-        <v>0.29285</v>
+        <v>0.05179999999999999</v>
       </c>
       <c r="F2">
-        <v>0.157</v>
+        <v>0.1675</v>
       </c>
       <c r="G2">
-        <v>0.07313435871742414</v>
+        <v>0.06416231285341234</v>
       </c>
       <c r="H2">
-        <v>0.07313435871742414</v>
+        <v>0.06416231285341234</v>
       </c>
       <c r="I2">
-        <v>0.04565196678260851</v>
+        <v>0.08581591042324026</v>
       </c>
       <c r="J2">
-        <v>0.03688251330371068</v>
+        <v>0.06810584149991791</v>
       </c>
       <c r="K2">
-        <v>3941.9</v>
+        <v>4818.9</v>
       </c>
       <c r="L2">
-        <v>0.04220047554355099</v>
+        <v>0.04427841862396836</v>
       </c>
       <c r="M2">
-        <v>2031.24</v>
+        <v>2245.97</v>
       </c>
       <c r="N2">
-        <v>0.0294317773475988</v>
+        <v>0.02636164528911342</v>
       </c>
       <c r="O2">
-        <v>0.5152946548618688</v>
+        <v>0.4660752453879517</v>
       </c>
       <c r="P2">
-        <v>2031.24</v>
+        <v>2245.97</v>
       </c>
       <c r="Q2">
-        <v>0.0294317773475988</v>
+        <v>0.02636164528911342</v>
       </c>
       <c r="R2">
-        <v>0.5152946548618688</v>
+        <v>0.4660752453879517</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7819.6</v>
+        <v>6978.9</v>
       </c>
       <c r="V2">
-        <v>0.1133025768236562</v>
+        <v>0.08191351011286598</v>
       </c>
       <c r="W2">
-        <v>0.08536112575074323</v>
+        <v>0.1829955955800394</v>
       </c>
       <c r="X2">
-        <v>0.1102545877570397</v>
+        <v>0.09267702671381534</v>
       </c>
       <c r="Y2">
-        <v>-0.02489346200629647</v>
+        <v>0.09031856886622402</v>
       </c>
       <c r="Z2">
-        <v>2.018443008187528</v>
+        <v>3.989230757952305</v>
       </c>
       <c r="AA2">
-        <v>0.08011572275217903</v>
+        <v>0.2797862671816128</v>
       </c>
       <c r="AB2">
-        <v>0.1004196396845229</v>
+        <v>0.08558483475567999</v>
       </c>
       <c r="AC2">
-        <v>-0.02030391693234391</v>
+        <v>0.1942014324259328</v>
       </c>
       <c r="AD2">
-        <v>9538.099999999999</v>
+        <v>10213.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9538.099999999999</v>
+        <v>10213.5</v>
       </c>
       <c r="AG2">
-        <v>1718.499999999998</v>
+        <v>3234.6</v>
       </c>
       <c r="AH2">
-        <v>0.1214220153704555</v>
+        <v>0.1070463956802034</v>
       </c>
       <c r="AI2">
-        <v>0.2426491164693372</v>
+        <v>0.2019324301881421</v>
       </c>
       <c r="AJ2">
-        <v>0.02429535002410447</v>
+        <v>0.03657684348602897</v>
       </c>
       <c r="AK2">
-        <v>0.05457530661890329</v>
+        <v>0.07418824355101733</v>
       </c>
       <c r="AL2">
-        <v>615.3</v>
+        <v>507.3</v>
       </c>
       <c r="AM2">
-        <v>615.3</v>
+        <v>507.3</v>
       </c>
       <c r="AN2">
-        <v>2.034968317296409</v>
+        <v>1.017950046843543</v>
       </c>
       <c r="AO2">
-        <v>6.93044043555989</v>
+        <v>18.41021092055983</v>
       </c>
       <c r="AP2">
-        <v>0.3666446203409354</v>
+        <v>0.322383239978472</v>
       </c>
       <c r="AQ2">
-        <v>6.93044043555989</v>
+        <v>18.41021092055983</v>
       </c>
     </row>
     <row r="3">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.121</v>
+        <v>0.125</v>
       </c>
       <c r="E3">
-        <v>0.0607</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="F3">
-        <v>0.17</v>
+        <v>0.228</v>
       </c>
       <c r="G3">
-        <v>0.07987798712460818</v>
+        <v>0.07408151144045028</v>
       </c>
       <c r="H3">
-        <v>0.07987798712460818</v>
+        <v>0.07408151144045028</v>
       </c>
       <c r="I3">
-        <v>0.06757895446425562</v>
+        <v>0.1215374607574172</v>
       </c>
       <c r="J3">
-        <v>0.05405747715859947</v>
+        <v>0.09870165690311092</v>
       </c>
       <c r="K3">
-        <v>1221.8</v>
+        <v>1788.6</v>
       </c>
       <c r="L3">
-        <v>0.04118103070545013</v>
+        <v>0.05058687105806488</v>
       </c>
       <c r="M3">
-        <v>532.2</v>
+        <v>574.4</v>
       </c>
       <c r="N3">
-        <v>0.02226023816196185</v>
+        <v>0.01992168668430855</v>
       </c>
       <c r="O3">
-        <v>0.4355868390898675</v>
+        <v>0.3211450296321145</v>
       </c>
       <c r="P3">
-        <v>532.2</v>
+        <v>574.4</v>
       </c>
       <c r="Q3">
-        <v>0.02226023816196185</v>
+        <v>0.01992168668430855</v>
       </c>
       <c r="R3">
-        <v>0.4355868390898675</v>
+        <v>0.3211450296321145</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1610.5</v>
+        <v>1142.7</v>
       </c>
       <c r="V3">
-        <v>0.06736210740293039</v>
+        <v>0.03963180949540282</v>
       </c>
       <c r="W3">
-        <v>0.09239820920805855</v>
+        <v>0.2210631697338986</v>
       </c>
       <c r="X3">
-        <v>0.1119088828634695</v>
+        <v>0.09422727219828618</v>
       </c>
       <c r="Y3">
-        <v>-0.01951067365541098</v>
+        <v>0.1268358975356124</v>
       </c>
       <c r="Z3">
-        <v>1.829838411249537</v>
+        <v>3.259971601910417</v>
       </c>
       <c r="AA3">
-        <v>0.09891644812004981</v>
+        <v>0.3217645985656469</v>
       </c>
       <c r="AB3">
-        <v>0.09976178170233886</v>
+        <v>0.0848498415080669</v>
       </c>
       <c r="AC3">
-        <v>-0.000845333582289054</v>
+        <v>0.23691475705758</v>
       </c>
       <c r="AD3">
-        <v>4445.9</v>
+        <v>5172.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4445.9</v>
+        <v>5172.2</v>
       </c>
       <c r="AG3">
-        <v>2835.4</v>
+        <v>4029.5</v>
       </c>
       <c r="AH3">
-        <v>0.1567997460675742</v>
+        <v>0.152100714304619</v>
       </c>
       <c r="AI3">
-        <v>0.3364588536227278</v>
+        <v>0.3177554016943842</v>
       </c>
       <c r="AJ3">
-        <v>0.1060220240432254</v>
+        <v>0.1226173377476995</v>
       </c>
       <c r="AK3">
-        <v>0.2443615178440616</v>
+        <v>0.2662442350640254</v>
       </c>
       <c r="AL3">
-        <v>289.7</v>
+        <v>206.7</v>
       </c>
       <c r="AM3">
-        <v>289.7</v>
+        <v>206.7</v>
       </c>
       <c r="AN3">
-        <v>2.026667274467794</v>
+        <v>1.134901478913416</v>
       </c>
       <c r="AO3">
-        <v>6.92095270969969</v>
+        <v>20.78955007256894</v>
       </c>
       <c r="AP3">
-        <v>1.292519487623649</v>
+        <v>0.884166410672752</v>
       </c>
       <c r="AQ3">
-        <v>6.92095270969969</v>
+        <v>20.78955007256894</v>
       </c>
     </row>
     <row r="4">
@@ -862,49 +862,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.03240000000000001</v>
+        <v>0.0549</v>
       </c>
       <c r="E4">
-        <v>0.525</v>
+        <v>0.0207</v>
       </c>
       <c r="F4">
-        <v>0.144</v>
+        <v>0.107</v>
       </c>
       <c r="G4">
-        <v>0.06999540319329023</v>
+        <v>0.05938906944966166</v>
       </c>
       <c r="H4">
-        <v>0.06999540319329023</v>
+        <v>0.05938906944966166</v>
       </c>
       <c r="I4">
-        <v>0.03544561569754581</v>
+        <v>0.06862625008846571</v>
       </c>
       <c r="J4">
-        <v>0.02891996515310861</v>
+        <v>0.05319532832474107</v>
       </c>
       <c r="K4">
-        <v>2720.1</v>
+        <v>3030.3</v>
       </c>
       <c r="L4">
-        <v>0.04267499635236328</v>
+        <v>0.04124271178689837</v>
       </c>
       <c r="M4">
-        <v>1499.04</v>
+        <v>1671.57</v>
       </c>
       <c r="N4">
-        <v>0.03323290568447097</v>
+        <v>0.02965590653857413</v>
       </c>
       <c r="O4">
-        <v>0.5510973861255102</v>
+        <v>0.5516186516186516</v>
       </c>
       <c r="P4">
-        <v>1499.04</v>
+        <v>1671.57</v>
       </c>
       <c r="Q4">
-        <v>0.03323290568447097</v>
+        <v>0.02965590653857413</v>
       </c>
       <c r="R4">
-        <v>0.5510973861255102</v>
+        <v>0.5516186516186516</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -913,73 +913,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6209.1</v>
+        <v>5836.2</v>
       </c>
       <c r="V4">
-        <v>0.1376523873181827</v>
+        <v>0.1035420603028448</v>
       </c>
       <c r="W4">
-        <v>0.07832404229342792</v>
+        <v>0.1449280214261801</v>
       </c>
       <c r="X4">
-        <v>0.1086002926506099</v>
+        <v>0.09112678122934449</v>
       </c>
       <c r="Y4">
-        <v>-0.03027625035718196</v>
+        <v>0.05380124019683562</v>
       </c>
       <c r="Z4">
-        <v>2.120161523698015</v>
+        <v>4.470466548224587</v>
       </c>
       <c r="AA4">
-        <v>0.06131499738430824</v>
+        <v>0.2378079357975788</v>
       </c>
       <c r="AB4">
-        <v>0.101077497666707</v>
+        <v>0.08631982800329308</v>
       </c>
       <c r="AC4">
-        <v>-0.03976250028239876</v>
+        <v>0.1514881077942857</v>
       </c>
       <c r="AD4">
-        <v>5092.2</v>
+        <v>5041.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5092.2</v>
+        <v>5041.3</v>
       </c>
       <c r="AG4">
-        <v>-1116.900000000001</v>
+        <v>-794.8999999999996</v>
       </c>
       <c r="AH4">
-        <v>0.1014396615092242</v>
+        <v>0.08209677104164359</v>
       </c>
       <c r="AI4">
-        <v>0.1951453185357778</v>
+        <v>0.1469702491144702</v>
       </c>
       <c r="AJ4">
-        <v>-0.02538974589795001</v>
+        <v>-0.01430432638841401</v>
       </c>
       <c r="AK4">
-        <v>-0.0561671184241626</v>
+        <v>-0.02792522826037314</v>
       </c>
       <c r="AL4">
-        <v>325.6</v>
+        <v>300.6</v>
       </c>
       <c r="AM4">
-        <v>325.6</v>
+        <v>300.6</v>
       </c>
       <c r="AN4">
-        <v>2.042271597016122</v>
+        <v>0.9206172388604822</v>
       </c>
       <c r="AO4">
-        <v>6.938882063882064</v>
+        <v>16.77411842980705</v>
       </c>
       <c r="AP4">
-        <v>-0.4479425683805248</v>
+        <v>-0.1451607012417823</v>
       </c>
       <c r="AQ4">
-        <v>6.938882063882064</v>
+        <v>16.77411842980705</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
@@ -588,49 +588,49 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08995</v>
+        <v>0.0395</v>
       </c>
       <c r="E2">
-        <v>0.05179999999999999</v>
+        <v>0.133</v>
       </c>
       <c r="F2">
-        <v>0.1675</v>
+        <v>0.11315</v>
       </c>
       <c r="G2">
-        <v>0.06416231285341234</v>
+        <v>0.09473108569135059</v>
       </c>
       <c r="H2">
-        <v>0.06416231285341234</v>
+        <v>0.09473108569135059</v>
       </c>
       <c r="I2">
-        <v>0.08581591042324026</v>
+        <v>0.1190848886213125</v>
       </c>
       <c r="J2">
-        <v>0.06810584149991791</v>
+        <v>0.104531779110969</v>
       </c>
       <c r="K2">
-        <v>4818.9</v>
+        <v>8872.200000000001</v>
       </c>
       <c r="L2">
-        <v>0.04427841862396836</v>
+        <v>0.08902468392534618</v>
       </c>
       <c r="M2">
-        <v>2245.97</v>
+        <v>2865.26</v>
       </c>
       <c r="N2">
-        <v>0.02636164528911342</v>
+        <v>0.02965177589224085</v>
       </c>
       <c r="O2">
-        <v>0.4660752453879517</v>
+        <v>0.3229480850296432</v>
       </c>
       <c r="P2">
-        <v>2245.97</v>
+        <v>2865.26</v>
       </c>
       <c r="Q2">
-        <v>0.02636164528911342</v>
+        <v>0.02965177589224085</v>
       </c>
       <c r="R2">
-        <v>0.4660752453879517</v>
+        <v>0.3229480850296432</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -639,73 +639,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>6978.9</v>
+        <v>9018.5</v>
       </c>
       <c r="V2">
-        <v>0.08191351011286598</v>
+        <v>0.09332993895289574</v>
       </c>
       <c r="W2">
-        <v>0.1829955955800394</v>
+        <v>0.2330578034700258</v>
       </c>
       <c r="X2">
-        <v>0.09267702671381534</v>
+        <v>0.09667327449743399</v>
       </c>
       <c r="Y2">
-        <v>0.09031856886622402</v>
+        <v>0.1363845289725918</v>
       </c>
       <c r="Z2">
-        <v>3.989230757952305</v>
+        <v>2.559184019351807</v>
       </c>
       <c r="AA2">
-        <v>0.2797862671816128</v>
+        <v>0.2585482548395369</v>
       </c>
       <c r="AB2">
-        <v>0.08558483475567999</v>
+        <v>0.08940359304465578</v>
       </c>
       <c r="AC2">
-        <v>0.1942014324259328</v>
+        <v>0.1691446617948811</v>
       </c>
       <c r="AD2">
-        <v>10213.5</v>
+        <v>12123.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10213.5</v>
+        <v>12123.4</v>
       </c>
       <c r="AG2">
-        <v>3234.6</v>
+        <v>3104.900000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1070463956802034</v>
+        <v>0.1114757474918095</v>
       </c>
       <c r="AI2">
-        <v>0.2019324301881421</v>
+        <v>0.2001439575787392</v>
       </c>
       <c r="AJ2">
-        <v>0.03657684348602897</v>
+        <v>0.03113143604264093</v>
       </c>
       <c r="AK2">
-        <v>0.07418824355101733</v>
+        <v>0.06022511924181797</v>
       </c>
       <c r="AL2">
-        <v>507.3</v>
+        <v>515.3</v>
       </c>
       <c r="AM2">
-        <v>507.3</v>
+        <v>515.3</v>
       </c>
       <c r="AN2">
-        <v>1.017950046843543</v>
+        <v>1.236627361377453</v>
       </c>
       <c r="AO2">
-        <v>18.41021092055983</v>
+        <v>23.03124393557151</v>
       </c>
       <c r="AP2">
-        <v>0.322383239978472</v>
+        <v>0.3167101880941696</v>
       </c>
       <c r="AQ2">
-        <v>18.41021092055983</v>
+        <v>23.03124393557151</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hannover Rück SE (XTRA:HNR1)</t>
+          <t>Münchener Rückversicherungs-Gesellschaft Aktiengesellschaft in München (XTRA:MUV2)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,49 +725,49 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.125</v>
+        <v>0.022</v>
       </c>
       <c r="E3">
-        <v>0.08289999999999999</v>
+        <v>0.156</v>
       </c>
       <c r="F3">
-        <v>0.228</v>
+        <v>0.13</v>
       </c>
       <c r="G3">
-        <v>0.07408151144045028</v>
+        <v>0.09807744318600914</v>
       </c>
       <c r="H3">
-        <v>0.07408151144045028</v>
+        <v>0.09807744318600914</v>
       </c>
       <c r="I3">
-        <v>0.1215374607574172</v>
+        <v>0.1180941334031411</v>
       </c>
       <c r="J3">
-        <v>0.09870165690311092</v>
+        <v>0.09999735119651891</v>
       </c>
       <c r="K3">
-        <v>1788.6</v>
+        <v>6362.9</v>
       </c>
       <c r="L3">
-        <v>0.05058687105806488</v>
+        <v>0.09202615475620567</v>
       </c>
       <c r="M3">
-        <v>574.4</v>
+        <v>2201.06</v>
       </c>
       <c r="N3">
-        <v>0.01992168668430855</v>
+        <v>0.03310342545690807</v>
       </c>
       <c r="O3">
-        <v>0.3211450296321145</v>
+        <v>0.3459208851309937</v>
       </c>
       <c r="P3">
-        <v>574.4</v>
+        <v>2201.06</v>
       </c>
       <c r="Q3">
-        <v>0.01992168668430855</v>
+        <v>0.03310342545690807</v>
       </c>
       <c r="R3">
-        <v>0.3211450296321145</v>
+        <v>0.3459208851309937</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -776,73 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1142.7</v>
+        <v>7276.4</v>
       </c>
       <c r="V3">
-        <v>0.03963180949540282</v>
+        <v>0.1094353470576204</v>
       </c>
       <c r="W3">
-        <v>0.2210631697338986</v>
+        <v>0.2184791715309921</v>
       </c>
       <c r="X3">
-        <v>0.09422727219828618</v>
+        <v>0.09556587416815106</v>
       </c>
       <c r="Y3">
-        <v>0.1268358975356124</v>
+        <v>0.122913297362841</v>
       </c>
       <c r="Z3">
-        <v>3.259971601910417</v>
+        <v>2.780998616384581</v>
       </c>
       <c r="AA3">
-        <v>0.3217645985656469</v>
+        <v>0.2780924953196421</v>
       </c>
       <c r="AB3">
-        <v>0.0848498415080669</v>
+        <v>0.08997009028871826</v>
       </c>
       <c r="AC3">
-        <v>0.23691475705758</v>
+        <v>0.1881224050309238</v>
       </c>
       <c r="AD3">
-        <v>5172.2</v>
+        <v>6927.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5172.2</v>
+        <v>6927.3</v>
       </c>
       <c r="AG3">
-        <v>4029.5</v>
+        <v>-349.0999999999995</v>
       </c>
       <c r="AH3">
-        <v>0.152100714304619</v>
+        <v>0.09435463110394361</v>
       </c>
       <c r="AI3">
-        <v>0.3177554016943842</v>
+        <v>0.1650327692714525</v>
       </c>
       <c r="AJ3">
-        <v>0.1226173377476995</v>
+        <v>-0.005278094019924004</v>
       </c>
       <c r="AK3">
-        <v>0.2662442350640254</v>
+        <v>-0.01006083766344176</v>
       </c>
       <c r="AL3">
-        <v>206.7</v>
+        <v>354.7</v>
       </c>
       <c r="AM3">
-        <v>206.7</v>
+        <v>354.7</v>
       </c>
       <c r="AN3">
-        <v>1.134901478913416</v>
+        <v>1.152475544020763</v>
       </c>
       <c r="AO3">
-        <v>20.78955007256894</v>
+        <v>23.0202988440936</v>
       </c>
       <c r="AP3">
-        <v>0.884166410672752</v>
+        <v>-0.05807879150861773</v>
       </c>
       <c r="AQ3">
-        <v>20.78955007256894</v>
+        <v>23.0202988440936</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft Aktiengesellschaft in München (XTRA:MUV2)</t>
+          <t>Hannover Rück SE (XTRA:HNR1)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,49 +862,49 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0549</v>
+        <v>0.057</v>
       </c>
       <c r="E4">
-        <v>0.0207</v>
+        <v>0.11</v>
       </c>
       <c r="F4">
-        <v>0.107</v>
+        <v>0.09630000000000001</v>
       </c>
       <c r="G4">
-        <v>0.05938906944966166</v>
+        <v>0.08714942476005727</v>
       </c>
       <c r="H4">
-        <v>0.05938906944966166</v>
+        <v>0.08714942476005727</v>
       </c>
       <c r="I4">
-        <v>0.06862625008846571</v>
+        <v>0.1213295890581531</v>
       </c>
       <c r="J4">
-        <v>0.05319532832474107</v>
+        <v>0.1102673144102108</v>
       </c>
       <c r="K4">
-        <v>3030.3</v>
+        <v>2509.3</v>
       </c>
       <c r="L4">
-        <v>0.04124271178689837</v>
+        <v>0.08222441402858013</v>
       </c>
       <c r="M4">
-        <v>1671.57</v>
+        <v>664.2</v>
       </c>
       <c r="N4">
-        <v>0.02965590653857413</v>
+        <v>0.02203723303660596</v>
       </c>
       <c r="O4">
-        <v>0.5516186516186516</v>
+        <v>0.2646953333599011</v>
       </c>
       <c r="P4">
-        <v>1671.57</v>
+        <v>664.2</v>
       </c>
       <c r="Q4">
-        <v>0.02965590653857413</v>
+        <v>0.02203723303660596</v>
       </c>
       <c r="R4">
-        <v>0.5516186516186516</v>
+        <v>0.2646953333599011</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -913,73 +913,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5836.2</v>
+        <v>1742.1</v>
       </c>
       <c r="V4">
-        <v>0.1035420603028448</v>
+        <v>0.05780045720125149</v>
       </c>
       <c r="W4">
-        <v>0.1449280214261801</v>
+        <v>0.2476364354090595</v>
       </c>
       <c r="X4">
-        <v>0.09112678122934449</v>
+        <v>0.0977806748267169</v>
       </c>
       <c r="Y4">
-        <v>0.05380124019683562</v>
+        <v>0.1498557605823426</v>
       </c>
       <c r="Z4">
-        <v>4.470466548224587</v>
+        <v>2.167496466544031</v>
       </c>
       <c r="AA4">
-        <v>0.2378079357975788</v>
+        <v>0.2390040143594318</v>
       </c>
       <c r="AB4">
-        <v>0.08631982800329308</v>
+        <v>0.0888370958005933</v>
       </c>
       <c r="AC4">
-        <v>0.1514881077942857</v>
+        <v>0.1501669185588385</v>
       </c>
       <c r="AD4">
-        <v>5041.3</v>
+        <v>5196.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>5041.3</v>
+        <v>5196.1</v>
       </c>
       <c r="AG4">
-        <v>-794.8999999999996</v>
+        <v>3454</v>
       </c>
       <c r="AH4">
-        <v>0.08209677104164359</v>
+        <v>0.1470483359746434</v>
       </c>
       <c r="AI4">
-        <v>0.1469702491144702</v>
+        <v>0.2793887547652718</v>
       </c>
       <c r="AJ4">
-        <v>-0.01430432638841401</v>
+        <v>0.1028162850993782</v>
       </c>
       <c r="AK4">
-        <v>-0.02792522826037314</v>
+        <v>0.2049121974371144</v>
       </c>
       <c r="AL4">
-        <v>300.6</v>
+        <v>160.6</v>
       </c>
       <c r="AM4">
-        <v>300.6</v>
+        <v>160.6</v>
       </c>
       <c r="AN4">
-        <v>0.9206172388604822</v>
+        <v>1.369990508331576</v>
       </c>
       <c r="AO4">
-        <v>16.77411842980705</v>
+        <v>23.05541718555417</v>
       </c>
       <c r="AP4">
-        <v>-0.1451607012417823</v>
+        <v>0.9106728538283063</v>
       </c>
       <c r="AQ4">
-        <v>16.77411842980705</v>
+        <v>23.05541718555417</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_reinsurance.xlsx
@@ -648,10 +648,10 @@
         <v>0.2330578034700258</v>
       </c>
       <c r="X2">
-        <v>0.09667327449743399</v>
+        <v>0.09664056750510198</v>
       </c>
       <c r="Y2">
-        <v>0.1363845289725918</v>
+        <v>0.1364172359649238</v>
       </c>
       <c r="Z2">
         <v>2.559184019351807</v>
@@ -660,10 +660,10 @@
         <v>0.2585482548395369</v>
       </c>
       <c r="AB2">
-        <v>0.08940359304465578</v>
+        <v>0.08937485259272417</v>
       </c>
       <c r="AC2">
-        <v>0.1691446617948811</v>
+        <v>0.1691734022468128</v>
       </c>
       <c r="AD2">
         <v>12123.4</v>
@@ -785,10 +785,10 @@
         <v>0.2184791715309921</v>
       </c>
       <c r="X3">
-        <v>0.09556587416815106</v>
+        <v>0.09553387913577124</v>
       </c>
       <c r="Y3">
-        <v>0.122913297362841</v>
+        <v>0.1229452923952208</v>
       </c>
       <c r="Z3">
         <v>2.780998616384581</v>
@@ -797,10 +797,10 @@
         <v>0.2780924953196421</v>
       </c>
       <c r="AB3">
-        <v>0.08997009028871826</v>
+        <v>0.08994111413581581</v>
       </c>
       <c r="AC3">
-        <v>0.1881224050309238</v>
+        <v>0.1881513811838263</v>
       </c>
       <c r="AD3">
         <v>6927.3</v>
@@ -922,10 +922,10 @@
         <v>0.2476364354090595</v>
       </c>
       <c r="X4">
-        <v>0.0977806748267169</v>
+        <v>0.09774725587443273</v>
       </c>
       <c r="Y4">
-        <v>0.1498557605823426</v>
+        <v>0.1498891795346268</v>
       </c>
       <c r="Z4">
         <v>2.167496466544031</v>
@@ -934,10 +934,10 @@
         <v>0.2390040143594318</v>
       </c>
       <c r="AB4">
-        <v>0.0888370958005933</v>
+        <v>0.08880859104963253</v>
       </c>
       <c r="AC4">
-        <v>0.1501669185588385</v>
+        <v>0.1501954233097992</v>
       </c>
       <c r="AD4">
         <v>5196.1</v>
